--- a/fhir/ig/cl-urgencia/0.2.0/StructureDefinition-bundle-alta-urgencia.xlsx
+++ b/fhir/ig/cl-urgencia/0.2.0/StructureDefinition-bundle-alta-urgencia.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9769" uniqueCount="549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9769" uniqueCount="551">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T11:47:41-03:00</t>
+    <t>2026-10-08T00:02:21-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Evento alta: el profesional da el alta de urgencia. Cierra el episodio (Encounter en finished) e informa diagnóstico de egreso, destino, medicamentos indicados y el documento clínico en PDF.</t>
+    <t>Evento alta: el profesional da el alta de urgencia. Cierra el episodio (Encounter en finished) e informa diagnóstico de egreso codificado en CIE-10, destino, medicamentos indicados y el documento clínico en PDF. Si el PDF aún no está disponible, el Bundle de alta se envía sin él y se reenvía completo cuando el PDF exista (el PUT condicional no duplica nada).</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -269,7 +269,7 @@
   </si>
   <si>
     <t>bdl-1:total only when a search or history {total.empty() or (type = 'searchset') or (type = 'history')}
-bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}urg-tx-put-condicional:Todas las entradas deben usar PUT condicional por identificador: request.method = PUT y request.url = [Tipo]?identifier=[system]|[value]. {entry.all(request.method = 'PUT' and request.url.contains('?identifier=') and request.url.contains('|'))}</t>
+bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}urg-tx-maestros:Patient, Organization y Practitioner se envían solo con creación condicional: request.method = POST, request.url = [Tipo] y request.ifNoneExist = identifier=[system]|[value]. Nunca se actualizan. {entry.where(resource is Patient or resource is Organization or resource is Practitioner).all(request.method = 'POST' and request.ifNoneExist.startsWith('identifier=') and request.ifNoneExist.contains('|'))}urg-tx-put-condicional:Los recursos del episodio (Encounter, Condition, MedicationRequest, DocumentReference) se envían con PUT condicional: request.method = PUT y request.url = [Tipo]?identifier=[system]|[value]. {entry.where((resource is Patient or resource is Organization or resource is Practitioner).not()).all(request.method = 'PUT' and request.url.contains('?identifier=') and request.url.contains('|'))}urg-tx-sin-id:Los recursos enviados con PUT condicional no llevan Resource.id: el id lo determina el servidor al encontrar (o crear) el recurso por su identificador. {entry.where(request.method = 'PUT').all(resource.id.empty())}urg-tx-identificador:El identificador de la operación condicional (request.url o request.ifNoneExist) debe ser el mismo que trae el recurso (identifier o masterIdentifier). {entry.where(request.method = 'PUT').select(request.url.substring(request.url.indexOf('|') + 1) in (resource.identifier.value | resource.masterIdentifier.value)).allTrue() and entry.where(request.method = 'POST').select(request.ifNoneExist.substring(request.ifNoneExist.indexOf('|') + 1) in resource.identifier.value).allTrue()}urg-tx-mismo-paciente:Todos los recursos del Bundle se refieren al mismo paciente: su subject apunta a la entrada del paciente. {(entry.resource.ofType(Encounter) | entry.resource.ofType(Condition) | entry.resource.ofType(MedicationRequest) | entry.resource.ofType(DocumentReference)).all(subject.reference = %resource.entry.where(resource is Patient).fullUrl.first())}urg-tx-restringido:Si el episodio está marcado como restringido (meta.security = R), también deben estarlo sus diagnósticos, indicaciones y documento. {entry.resource.ofType(Encounter).meta.security.where(code = 'R').exists() implies (entry.resource.ofType(Condition) | entry.resource.ofType(MedicationRequest) | entry.resource.ofType(DocumentReference)).all(meta.security.where(system = 'http://terminology.hl7.org/CodeSystem/v3-Confidentiality' and code = 'R').exists())}urg-alta-cie10:En el alta, todo diagnóstico debe venir codificado en CIE-10. {entry.resource.ofType(Condition).all(code.coding.where(system = 'http://hl7.org/fhir/sid/icd-10').exists())}urg-alta-documento:En el alta, el documento es un resumen de alta de urgencia (LOINC 59258-4). {entry.resource.ofType(DocumentReference).all(type.coding.where(system = 'http://loinc.org' and code = '59258-4').exists())}</t>
   </si>
   <si>
     <t>N/A</t>
@@ -570,10 +570,10 @@
     <t>Bundle.entry</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>Entrada: recurso más su PUT condicional</t>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Entrada: recurso más su operación condicional</t>
   </si>
   <si>
     <t>An entry in a bundle resource - will either contain a resource or information about a resource (transactions and history only).</t>
@@ -696,7 +696,7 @@
     <t>Bundle.entry.request</t>
   </si>
   <si>
-    <t>Operación: PUT condicional por identificador</t>
+    <t>POST con ifNoneExist (maestros) o PUT condicional (episodio)</t>
   </si>
   <si>
     <t>Additional information about how this entry should be processed as part of a transaction or batch.  For history, it shows how the entry was processed to create the version contained in the entry.</t>
@@ -718,7 +718,7 @@
     <t>Bundle.entry.request.method</t>
   </si>
   <si>
-    <t>PUT</t>
+    <t>POST (maestros) | PUT (episodio)</t>
   </si>
   <si>
     <t>In a transaction or batch, this is the HTTP action to be executed for this entry. In a history bundle, this indicates the HTTP action that occurred.</t>
@@ -733,7 +733,7 @@
     <t>Bundle.entry.request.url</t>
   </si>
   <si>
-    <t>[Tipo]?identifier=[system]|[value]</t>
+    <t>[Tipo] (maestros) o [Tipo]?identifier=[sistema]|[valor] (episodio)</t>
   </si>
   <si>
     <t>The URL for this entry, relative to the root (the address to which the request is posted).</t>
@@ -769,7 +769,7 @@
     <t>Bundle.entry.request.ifNoneExist</t>
   </si>
   <si>
-    <t>For conditional creates</t>
+    <t>identifier=[sistema]|[valor] (solo maestros)</t>
   </si>
   <si>
     <t>Instruct the server not to perform the create if a specified resource already exists. For further information, see the API documentation for ["Conditional Create"](http://hl7.org/fhir/R4/http.html#ccreate). This is just the query portion of the URL - what follows the "?" (not including the "?").</t>
@@ -920,7 +920,7 @@
     <t>Bundle.entry:paciente.request</t>
   </si>
   <si>
-    <t>PUT Patient?identifier=[sistema]|[valor]</t>
+    <t>POST Patient, ifNoneExist identifier=[sistema]|[valor]</t>
   </si>
   <si>
     <t>Bundle.entry:paciente.request.id</t>
@@ -933,6 +933,9 @@
   </si>
   <si>
     <t>Bundle.entry:paciente.request.method</t>
+  </si>
+  <si>
+    <t>POST</t>
   </si>
   <si>
     <t>Bundle.entry:paciente.request.url</t>
@@ -1041,7 +1044,7 @@
     <t>Bundle.entry:establecimiento.request</t>
   </si>
   <si>
-    <t>PUT Organization?identifier=[sistema DEIS]|[código]</t>
+    <t>POST Organization, ifNoneExist identifier=[sistema DEIS]|[código]</t>
   </si>
   <si>
     <t>Bundle.entry:establecimiento.request.id</t>
@@ -1162,7 +1165,7 @@
     <t>Bundle.entry:profesional.request</t>
   </si>
   <si>
-    <t>PUT Practitioner?identifier=[sistema]|[RUN]</t>
+    <t>POST Practitioner, ifNoneExist identifier=[sistema]|[RUN]</t>
   </si>
   <si>
     <t>Bundle.entry:profesional.request.id</t>
@@ -1254,7 +1257,7 @@
 </t>
   </si>
   <si>
-    <t>An interaction between a patient and healthcare provider(s) for the purpose of providing healthcare service(s) or assessing the health status of a patient.</t>
+    <t>Episodio de atención en una unidad de urgencia. Se envía SIEMPRE COMPLETO en cada evento: el PUT condicional reemplaza el recurso entero, por lo que el alta y el abandono deben repetir todos los datos informados en la admisión (previsión, procedencia, medio de llegada, motivo de consulta, etc.). Un dato omitido en el alta se borra del repositorio.</t>
   </si>
   <si>
     <t>Encounter[@moodCode='EVN']</t>
@@ -1294,6 +1297,9 @@
   </si>
   <si>
     <t>Bundle.entry:encuentro.request.method</t>
+  </si>
+  <si>
+    <t>PUT</t>
   </si>
   <si>
     <t>Bundle.entry:encuentro.request.url</t>
@@ -5869,7 +5875,7 @@
         <v>77</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>221</v>
+        <v>77</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>77</v>
@@ -9493,7 +9499,7 @@
         <v>77</v>
       </c>
       <c r="S66" t="s" s="2">
-        <v>221</v>
+        <v>292</v>
       </c>
       <c r="T66" t="s" s="2">
         <v>77</v>
@@ -9561,7 +9567,7 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>225</v>
@@ -9675,7 +9681,7 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B68" t="s" s="2">
         <v>229</v>
@@ -9787,7 +9793,7 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>232</v>
@@ -9899,7 +9905,7 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>234</v>
@@ -10011,7 +10017,7 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>237</v>
@@ -10022,7 +10028,7 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G71" t="s" s="2">
         <v>87</v>
@@ -10123,7 +10129,7 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>240</v>
@@ -10235,7 +10241,7 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B73" t="s" s="2">
         <v>244</v>
@@ -10347,7 +10353,7 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B74" t="s" s="2">
         <v>245</v>
@@ -10461,7 +10467,7 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B75" t="s" s="2">
         <v>246</v>
@@ -10577,7 +10583,7 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>247</v>
@@ -10689,7 +10695,7 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>250</v>
@@ -10801,7 +10807,7 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>253</v>
@@ -10915,7 +10921,7 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>257</v>
@@ -11029,7 +11035,7 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>261</v>
@@ -11143,13 +11149,13 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>174</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D81" t="s" s="2">
         <v>77</v>
@@ -11174,7 +11180,7 @@
         <v>144</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M81" t="s" s="2">
         <v>177</v>
@@ -11257,7 +11263,7 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>181</v>
@@ -11369,7 +11375,7 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B83" t="s" s="2">
         <v>182</v>
@@ -11483,7 +11489,7 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B84" t="s" s="2">
         <v>183</v>
@@ -11599,7 +11605,7 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B85" t="s" s="2">
         <v>184</v>
@@ -11711,7 +11717,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B86" t="s" s="2">
         <v>187</v>
@@ -11825,7 +11831,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B87" t="s" s="2">
         <v>191</v>
@@ -11851,13 +11857,13 @@
         <v>77</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -11923,10 +11929,10 @@
         <v>77</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>77</v>
@@ -11937,7 +11943,7 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>195</v>
@@ -12049,7 +12055,7 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>199</v>
@@ -12161,7 +12167,7 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>200</v>
@@ -12275,7 +12281,7 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>201</v>
@@ -12391,7 +12397,7 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B92" t="s" s="2">
         <v>202</v>
@@ -12505,7 +12511,7 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B93" t="s" s="2">
         <v>208</v>
@@ -12619,7 +12625,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>213</v>
@@ -12648,7 +12654,7 @@
         <v>144</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M94" t="s" s="2">
         <v>215</v>
@@ -12731,7 +12737,7 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>217</v>
@@ -12843,7 +12849,7 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>218</v>
@@ -12957,7 +12963,7 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>219</v>
@@ -13073,7 +13079,7 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>220</v>
@@ -13117,7 +13123,7 @@
         <v>77</v>
       </c>
       <c r="S98" t="s" s="2">
-        <v>221</v>
+        <v>292</v>
       </c>
       <c r="T98" t="s" s="2">
         <v>77</v>
@@ -13185,7 +13191,7 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>225</v>
@@ -13299,7 +13305,7 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>229</v>
@@ -13411,7 +13417,7 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>232</v>
@@ -13523,7 +13529,7 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>234</v>
@@ -13635,7 +13641,7 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>237</v>
@@ -13646,7 +13652,7 @@
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G103" t="s" s="2">
         <v>87</v>
@@ -13747,7 +13753,7 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>240</v>
@@ -13859,7 +13865,7 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>244</v>
@@ -13971,7 +13977,7 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>245</v>
@@ -14085,7 +14091,7 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>246</v>
@@ -14201,7 +14207,7 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>247</v>
@@ -14313,7 +14319,7 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>250</v>
@@ -14425,7 +14431,7 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B110" t="s" s="2">
         <v>253</v>
@@ -14539,7 +14545,7 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B111" t="s" s="2">
         <v>257</v>
@@ -14653,7 +14659,7 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>261</v>
@@ -14767,13 +14773,13 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>174</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D113" t="s" s="2">
         <v>77</v>
@@ -14798,7 +14804,7 @@
         <v>144</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M113" t="s" s="2">
         <v>177</v>
@@ -14881,7 +14887,7 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>181</v>
@@ -14993,7 +14999,7 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>182</v>
@@ -15107,7 +15113,7 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B116" t="s" s="2">
         <v>183</v>
@@ -15223,7 +15229,7 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>184</v>
@@ -15335,7 +15341,7 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>187</v>
@@ -15449,7 +15455,7 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>191</v>
@@ -15475,13 +15481,13 @@
         <v>77</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -15547,10 +15553,10 @@
         <v>77</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>77</v>
@@ -15561,7 +15567,7 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>195</v>
@@ -15673,7 +15679,7 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>199</v>
@@ -15785,7 +15791,7 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>200</v>
@@ -15899,7 +15905,7 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>201</v>
@@ -16015,7 +16021,7 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B124" t="s" s="2">
         <v>202</v>
@@ -16129,7 +16135,7 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>208</v>
@@ -16243,7 +16249,7 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>213</v>
@@ -16272,7 +16278,7 @@
         <v>144</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M126" t="s" s="2">
         <v>215</v>
@@ -16355,7 +16361,7 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B127" t="s" s="2">
         <v>217</v>
@@ -16467,7 +16473,7 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B128" t="s" s="2">
         <v>218</v>
@@ -16581,7 +16587,7 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B129" t="s" s="2">
         <v>219</v>
@@ -16697,7 +16703,7 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>220</v>
@@ -16741,7 +16747,7 @@
         <v>77</v>
       </c>
       <c r="S130" t="s" s="2">
-        <v>221</v>
+        <v>292</v>
       </c>
       <c r="T130" t="s" s="2">
         <v>77</v>
@@ -16809,7 +16815,7 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B131" t="s" s="2">
         <v>225</v>
@@ -16923,7 +16929,7 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B132" t="s" s="2">
         <v>229</v>
@@ -17035,7 +17041,7 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B133" t="s" s="2">
         <v>232</v>
@@ -17147,7 +17153,7 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B134" t="s" s="2">
         <v>234</v>
@@ -17259,7 +17265,7 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B135" t="s" s="2">
         <v>237</v>
@@ -17270,7 +17276,7 @@
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G135" t="s" s="2">
         <v>87</v>
@@ -17371,7 +17377,7 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B136" t="s" s="2">
         <v>240</v>
@@ -17483,7 +17489,7 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B137" t="s" s="2">
         <v>244</v>
@@ -17595,7 +17601,7 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B138" t="s" s="2">
         <v>245</v>
@@ -17709,7 +17715,7 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B139" t="s" s="2">
         <v>246</v>
@@ -17825,7 +17831,7 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B140" t="s" s="2">
         <v>247</v>
@@ -17937,7 +17943,7 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B141" t="s" s="2">
         <v>250</v>
@@ -18049,7 +18055,7 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B142" t="s" s="2">
         <v>253</v>
@@ -18163,7 +18169,7 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B143" t="s" s="2">
         <v>257</v>
@@ -18277,7 +18283,7 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B144" t="s" s="2">
         <v>261</v>
@@ -18391,13 +18397,13 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B145" t="s" s="2">
         <v>174</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D145" t="s" s="2">
         <v>77</v>
@@ -18422,7 +18428,7 @@
         <v>144</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M145" t="s" s="2">
         <v>177</v>
@@ -18505,7 +18511,7 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B146" t="s" s="2">
         <v>181</v>
@@ -18617,7 +18623,7 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B147" t="s" s="2">
         <v>182</v>
@@ -18731,7 +18737,7 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B148" t="s" s="2">
         <v>183</v>
@@ -18847,7 +18853,7 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B149" t="s" s="2">
         <v>184</v>
@@ -18959,7 +18965,7 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B150" t="s" s="2">
         <v>187</v>
@@ -19073,14 +19079,14 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B151" t="s" s="2">
         <v>191</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
@@ -19099,13 +19105,13 @@
         <v>77</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
@@ -19174,7 +19180,7 @@
         <v>77</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AM151" t="s" s="2">
         <v>77</v>
@@ -19185,7 +19191,7 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B152" t="s" s="2">
         <v>195</v>
@@ -19297,7 +19303,7 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B153" t="s" s="2">
         <v>199</v>
@@ -19409,7 +19415,7 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B154" t="s" s="2">
         <v>200</v>
@@ -19523,7 +19529,7 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B155" t="s" s="2">
         <v>201</v>
@@ -19639,7 +19645,7 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B156" t="s" s="2">
         <v>202</v>
@@ -19753,7 +19759,7 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B157" t="s" s="2">
         <v>208</v>
@@ -19867,7 +19873,7 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B158" t="s" s="2">
         <v>213</v>
@@ -19896,7 +19902,7 @@
         <v>144</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M158" t="s" s="2">
         <v>215</v>
@@ -19979,7 +19985,7 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B159" t="s" s="2">
         <v>217</v>
@@ -20091,7 +20097,7 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B160" t="s" s="2">
         <v>218</v>
@@ -20205,7 +20211,7 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B161" t="s" s="2">
         <v>219</v>
@@ -20321,7 +20327,7 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B162" t="s" s="2">
         <v>220</v>
@@ -20365,7 +20371,7 @@
         <v>77</v>
       </c>
       <c r="S162" t="s" s="2">
-        <v>221</v>
+        <v>412</v>
       </c>
       <c r="T162" t="s" s="2">
         <v>77</v>
@@ -20433,7 +20439,7 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B163" t="s" s="2">
         <v>225</v>
@@ -20547,7 +20553,7 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B164" t="s" s="2">
         <v>229</v>
@@ -20659,7 +20665,7 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B165" t="s" s="2">
         <v>232</v>
@@ -20771,7 +20777,7 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B166" t="s" s="2">
         <v>234</v>
@@ -20883,7 +20889,7 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B167" t="s" s="2">
         <v>237</v>
@@ -20995,7 +21001,7 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B168" t="s" s="2">
         <v>240</v>
@@ -21107,7 +21113,7 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B169" t="s" s="2">
         <v>244</v>
@@ -21219,7 +21225,7 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B170" t="s" s="2">
         <v>245</v>
@@ -21333,7 +21339,7 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B171" t="s" s="2">
         <v>246</v>
@@ -21449,7 +21455,7 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B172" t="s" s="2">
         <v>247</v>
@@ -21561,7 +21567,7 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B173" t="s" s="2">
         <v>250</v>
@@ -21673,7 +21679,7 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B174" t="s" s="2">
         <v>253</v>
@@ -21787,7 +21793,7 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B175" t="s" s="2">
         <v>257</v>
@@ -21901,7 +21907,7 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B176" t="s" s="2">
         <v>261</v>
@@ -22015,13 +22021,13 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B177" t="s" s="2">
         <v>174</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D177" t="s" s="2">
         <v>77</v>
@@ -22046,7 +22052,7 @@
         <v>144</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="M177" t="s" s="2">
         <v>177</v>
@@ -22129,7 +22135,7 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B178" t="s" s="2">
         <v>181</v>
@@ -22241,7 +22247,7 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B179" t="s" s="2">
         <v>182</v>
@@ -22355,7 +22361,7 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B180" t="s" s="2">
         <v>183</v>
@@ -22471,7 +22477,7 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B181" t="s" s="2">
         <v>184</v>
@@ -22583,7 +22589,7 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B182" t="s" s="2">
         <v>187</v>
@@ -22697,7 +22703,7 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B183" t="s" s="2">
         <v>191</v>
@@ -22723,13 +22729,13 @@
         <v>77</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" s="2"/>
@@ -22795,10 +22801,10 @@
         <v>77</v>
       </c>
       <c r="AK183" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AL183" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AM183" t="s" s="2">
         <v>77</v>
@@ -22809,7 +22815,7 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B184" t="s" s="2">
         <v>195</v>
@@ -22921,7 +22927,7 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B185" t="s" s="2">
         <v>199</v>
@@ -23033,7 +23039,7 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B186" t="s" s="2">
         <v>200</v>
@@ -23147,7 +23153,7 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B187" t="s" s="2">
         <v>201</v>
@@ -23263,7 +23269,7 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B188" t="s" s="2">
         <v>202</v>
@@ -23377,7 +23383,7 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B189" t="s" s="2">
         <v>208</v>
@@ -23491,7 +23497,7 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B190" t="s" s="2">
         <v>213</v>
@@ -23520,7 +23526,7 @@
         <v>144</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="M190" t="s" s="2">
         <v>215</v>
@@ -23603,7 +23609,7 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B191" t="s" s="2">
         <v>217</v>
@@ -23715,7 +23721,7 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B192" t="s" s="2">
         <v>218</v>
@@ -23829,7 +23835,7 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B193" t="s" s="2">
         <v>219</v>
@@ -23945,7 +23951,7 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B194" t="s" s="2">
         <v>220</v>
@@ -23989,7 +23995,7 @@
         <v>77</v>
       </c>
       <c r="S194" t="s" s="2">
-        <v>221</v>
+        <v>412</v>
       </c>
       <c r="T194" t="s" s="2">
         <v>77</v>
@@ -24057,7 +24063,7 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B195" t="s" s="2">
         <v>225</v>
@@ -24171,7 +24177,7 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B196" t="s" s="2">
         <v>229</v>
@@ -24283,7 +24289,7 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B197" t="s" s="2">
         <v>232</v>
@@ -24395,7 +24401,7 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B198" t="s" s="2">
         <v>234</v>
@@ -24507,7 +24513,7 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B199" t="s" s="2">
         <v>237</v>
@@ -24619,7 +24625,7 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B200" t="s" s="2">
         <v>240</v>
@@ -24731,7 +24737,7 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B201" t="s" s="2">
         <v>244</v>
@@ -24843,7 +24849,7 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B202" t="s" s="2">
         <v>245</v>
@@ -24957,7 +24963,7 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B203" t="s" s="2">
         <v>246</v>
@@ -25073,7 +25079,7 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B204" t="s" s="2">
         <v>247</v>
@@ -25185,7 +25191,7 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B205" t="s" s="2">
         <v>250</v>
@@ -25297,7 +25303,7 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B206" t="s" s="2">
         <v>253</v>
@@ -25411,7 +25417,7 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B207" t="s" s="2">
         <v>257</v>
@@ -25525,7 +25531,7 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B208" t="s" s="2">
         <v>261</v>
@@ -25639,13 +25645,13 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B209" t="s" s="2">
         <v>174</v>
       </c>
       <c r="C209" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="D209" t="s" s="2">
         <v>77</v>
@@ -25670,7 +25676,7 @@
         <v>144</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="M209" t="s" s="2">
         <v>177</v>
@@ -25753,7 +25759,7 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B210" t="s" s="2">
         <v>181</v>
@@ -25865,7 +25871,7 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B211" t="s" s="2">
         <v>182</v>
@@ -25979,7 +25985,7 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B212" t="s" s="2">
         <v>183</v>
@@ -26095,7 +26101,7 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B213" t="s" s="2">
         <v>184</v>
@@ -26207,7 +26213,7 @@
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B214" t="s" s="2">
         <v>187</v>
@@ -26321,14 +26327,14 @@
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B215" t="s" s="2">
         <v>191</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="E215" s="2"/>
       <c r="F215" t="s" s="2">
@@ -26347,13 +26353,13 @@
         <v>77</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="N215" s="2"/>
       <c r="O215" s="2"/>
@@ -26422,7 +26428,7 @@
         <v>77</v>
       </c>
       <c r="AL215" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AM215" t="s" s="2">
         <v>77</v>
@@ -26433,7 +26439,7 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B216" t="s" s="2">
         <v>195</v>
@@ -26545,7 +26551,7 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B217" t="s" s="2">
         <v>199</v>
@@ -26657,7 +26663,7 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B218" t="s" s="2">
         <v>200</v>
@@ -26771,7 +26777,7 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B219" t="s" s="2">
         <v>201</v>
@@ -26887,7 +26893,7 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B220" t="s" s="2">
         <v>202</v>
@@ -27001,7 +27007,7 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B221" t="s" s="2">
         <v>208</v>
@@ -27115,7 +27121,7 @@
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B222" t="s" s="2">
         <v>213</v>
@@ -27144,7 +27150,7 @@
         <v>144</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="M222" t="s" s="2">
         <v>215</v>
@@ -27227,7 +27233,7 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B223" t="s" s="2">
         <v>217</v>
@@ -27339,7 +27345,7 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B224" t="s" s="2">
         <v>218</v>
@@ -27453,7 +27459,7 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B225" t="s" s="2">
         <v>219</v>
@@ -27569,7 +27575,7 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B226" t="s" s="2">
         <v>220</v>
@@ -27613,7 +27619,7 @@
         <v>77</v>
       </c>
       <c r="S226" t="s" s="2">
-        <v>221</v>
+        <v>412</v>
       </c>
       <c r="T226" t="s" s="2">
         <v>77</v>
@@ -27681,7 +27687,7 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B227" t="s" s="2">
         <v>225</v>
@@ -27795,7 +27801,7 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B228" t="s" s="2">
         <v>229</v>
@@ -27907,7 +27913,7 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B229" t="s" s="2">
         <v>232</v>
@@ -28019,7 +28025,7 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B230" t="s" s="2">
         <v>234</v>
@@ -28131,7 +28137,7 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B231" t="s" s="2">
         <v>237</v>
@@ -28243,7 +28249,7 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B232" t="s" s="2">
         <v>240</v>
@@ -28355,7 +28361,7 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B233" t="s" s="2">
         <v>244</v>
@@ -28467,7 +28473,7 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B234" t="s" s="2">
         <v>245</v>
@@ -28581,7 +28587,7 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B235" t="s" s="2">
         <v>246</v>
@@ -28697,7 +28703,7 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B236" t="s" s="2">
         <v>247</v>
@@ -28809,7 +28815,7 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B237" t="s" s="2">
         <v>250</v>
@@ -28921,7 +28927,7 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B238" t="s" s="2">
         <v>253</v>
@@ -29035,7 +29041,7 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B239" t="s" s="2">
         <v>257</v>
@@ -29149,7 +29155,7 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B240" t="s" s="2">
         <v>261</v>
@@ -29263,20 +29269,20 @@
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B241" t="s" s="2">
         <v>174</v>
       </c>
       <c r="C241" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="D241" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E241" s="2"/>
       <c r="F241" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G241" t="s" s="2">
         <v>87</v>
@@ -29294,7 +29300,7 @@
         <v>144</v>
       </c>
       <c r="L241" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="M241" t="s" s="2">
         <v>177</v>
@@ -29377,7 +29383,7 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B242" t="s" s="2">
         <v>181</v>
@@ -29489,7 +29495,7 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B243" t="s" s="2">
         <v>182</v>
@@ -29603,7 +29609,7 @@
     </row>
     <row r="244" hidden="true">
       <c r="A244" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B244" t="s" s="2">
         <v>183</v>
@@ -29719,7 +29725,7 @@
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B245" t="s" s="2">
         <v>184</v>
@@ -29831,7 +29837,7 @@
     </row>
     <row r="246">
       <c r="A246" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B246" t="s" s="2">
         <v>187</v>
@@ -29945,7 +29951,7 @@
     </row>
     <row r="247">
       <c r="A247" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B247" t="s" s="2">
         <v>191</v>
@@ -29971,16 +29977,16 @@
         <v>77</v>
       </c>
       <c r="K247" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="L247" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="M247" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="N247" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="O247" s="2"/>
       <c r="P247" t="s" s="2">
@@ -30048,10 +30054,10 @@
         <v>77</v>
       </c>
       <c r="AL247" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="AM247" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AN247" t="s" s="2">
         <v>77</v>
@@ -30059,7 +30065,7 @@
     </row>
     <row r="248" hidden="true">
       <c r="A248" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B248" t="s" s="2">
         <v>195</v>
@@ -30171,7 +30177,7 @@
     </row>
     <row r="249" hidden="true">
       <c r="A249" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B249" t="s" s="2">
         <v>199</v>
@@ -30283,7 +30289,7 @@
     </row>
     <row r="250" hidden="true">
       <c r="A250" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B250" t="s" s="2">
         <v>200</v>
@@ -30397,7 +30403,7 @@
     </row>
     <row r="251" hidden="true">
       <c r="A251" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B251" t="s" s="2">
         <v>201</v>
@@ -30513,7 +30519,7 @@
     </row>
     <row r="252" hidden="true">
       <c r="A252" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B252" t="s" s="2">
         <v>202</v>
@@ -30627,7 +30633,7 @@
     </row>
     <row r="253" hidden="true">
       <c r="A253" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B253" t="s" s="2">
         <v>208</v>
@@ -30741,7 +30747,7 @@
     </row>
     <row r="254">
       <c r="A254" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B254" t="s" s="2">
         <v>213</v>
@@ -30770,7 +30776,7 @@
         <v>144</v>
       </c>
       <c r="L254" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="M254" t="s" s="2">
         <v>215</v>
@@ -30853,7 +30859,7 @@
     </row>
     <row r="255" hidden="true">
       <c r="A255" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B255" t="s" s="2">
         <v>217</v>
@@ -30965,7 +30971,7 @@
     </row>
     <row r="256" hidden="true">
       <c r="A256" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B256" t="s" s="2">
         <v>218</v>
@@ -31079,7 +31085,7 @@
     </row>
     <row r="257" hidden="true">
       <c r="A257" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B257" t="s" s="2">
         <v>219</v>
@@ -31195,7 +31201,7 @@
     </row>
     <row r="258" hidden="true">
       <c r="A258" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B258" t="s" s="2">
         <v>220</v>
@@ -31239,7 +31245,7 @@
         <v>77</v>
       </c>
       <c r="S258" t="s" s="2">
-        <v>221</v>
+        <v>412</v>
       </c>
       <c r="T258" t="s" s="2">
         <v>77</v>
@@ -31307,7 +31313,7 @@
     </row>
     <row r="259" hidden="true">
       <c r="A259" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B259" t="s" s="2">
         <v>225</v>
@@ -31421,7 +31427,7 @@
     </row>
     <row r="260" hidden="true">
       <c r="A260" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B260" t="s" s="2">
         <v>229</v>
@@ -31533,7 +31539,7 @@
     </row>
     <row r="261" hidden="true">
       <c r="A261" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B261" t="s" s="2">
         <v>232</v>
@@ -31645,7 +31651,7 @@
     </row>
     <row r="262" hidden="true">
       <c r="A262" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B262" t="s" s="2">
         <v>234</v>
@@ -31757,7 +31763,7 @@
     </row>
     <row r="263" hidden="true">
       <c r="A263" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B263" t="s" s="2">
         <v>237</v>
@@ -31869,7 +31875,7 @@
     </row>
     <row r="264" hidden="true">
       <c r="A264" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B264" t="s" s="2">
         <v>240</v>
@@ -31981,7 +31987,7 @@
     </row>
     <row r="265" hidden="true">
       <c r="A265" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B265" t="s" s="2">
         <v>244</v>
@@ -32093,7 +32099,7 @@
     </row>
     <row r="266" hidden="true">
       <c r="A266" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B266" t="s" s="2">
         <v>245</v>
@@ -32207,7 +32213,7 @@
     </row>
     <row r="267" hidden="true">
       <c r="A267" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B267" t="s" s="2">
         <v>246</v>
@@ -32323,7 +32329,7 @@
     </row>
     <row r="268" hidden="true">
       <c r="A268" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B268" t="s" s="2">
         <v>247</v>
@@ -32435,7 +32441,7 @@
     </row>
     <row r="269" hidden="true">
       <c r="A269" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B269" t="s" s="2">
         <v>250</v>
@@ -32547,7 +32553,7 @@
     </row>
     <row r="270" hidden="true">
       <c r="A270" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B270" t="s" s="2">
         <v>253</v>
@@ -32661,7 +32667,7 @@
     </row>
     <row r="271" hidden="true">
       <c r="A271" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B271" t="s" s="2">
         <v>257</v>
@@ -32775,7 +32781,7 @@
     </row>
     <row r="272" hidden="true">
       <c r="A272" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B272" t="s" s="2">
         <v>261</v>
@@ -32889,10 +32895,10 @@
     </row>
     <row r="273" hidden="true">
       <c r="A273" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C273" s="2"/>
       <c r="D273" t="s" s="2">
@@ -32915,19 +32921,19 @@
         <v>88</v>
       </c>
       <c r="K273" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="L273" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="M273" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="N273" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="O273" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="P273" t="s" s="2">
         <v>77</v>
@@ -32976,7 +32982,7 @@
         <v>77</v>
       </c>
       <c r="AF273" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="AG273" t="s" s="2">
         <v>78</v>
